--- a/pre-processing/cluster_representatives.xlsx
+++ b/pre-processing/cluster_representatives.xlsx
@@ -28,169 +28,169 @@
     <t>images_png/phone/277360579.png</t>
   </si>
   <si>
+    <t>images_png/laptop/278071899.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/275646608.png</t>
+  </si>
+  <si>
     <t>images_png/laptop/278226504.png</t>
   </si>
   <si>
-    <t>images_png/laptop/278071899.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/274877090.png</t>
+    <t>images_png/speaker/276075466.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/276931435.png</t>
   </si>
   <si>
     <t>images_png/laptop/278078281.png</t>
   </si>
   <si>
+    <t>images_png/camera/274879959.png</t>
+  </si>
+  <si>
+    <t>images_png/laptop/277961929.png</t>
+  </si>
+  <si>
     <t>images_png/phone/277646748.png</t>
   </si>
   <si>
-    <t>images_png/camera/274879959.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/276387015.png</t>
-  </si>
-  <si>
-    <t>images_png/speaker/241639907.png</t>
-  </si>
-  <si>
     <t>images_png/camera/270977170.png</t>
   </si>
   <si>
+    <t>images_png/phone/275510578.png</t>
+  </si>
+  <si>
+    <t>images_png/phone/277777809.png</t>
+  </si>
+  <si>
+    <t>images_png/camera/272268455.png</t>
+  </si>
+  <si>
+    <t>images_png/camera/263596152.png</t>
+  </si>
+  <si>
+    <t>images_png/laptop/275382480.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/276379164.png</t>
+  </si>
+  <si>
     <t>images_png/tv/275803796.png</t>
   </si>
   <si>
-    <t>images_png/tv/276379164.png</t>
-  </si>
-  <si>
-    <t>images_png/phone/275510578.png</t>
-  </si>
-  <si>
     <t>images_png/phone/277164932.png</t>
   </si>
   <si>
-    <t>images_png/phone/277777809.png</t>
-  </si>
-  <si>
-    <t>images_png/camera/263596152.png</t>
-  </si>
-  <si>
-    <t>images_png/camera/272268455.png</t>
+    <t>images_png/tv/275244717.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/278077419.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/277991140.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/277989480.png</t>
   </si>
   <si>
     <t>images_png/tv/277988926.png</t>
   </si>
   <si>
+    <t>images_png/tv/277972475.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/276861683.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/276621107.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/276921311.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/275245456.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/276268195.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/275269812.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/275019168.png</t>
+  </si>
+  <si>
+    <t>images_png/tv/248237801.png</t>
+  </si>
+  <si>
+    <t>images_png/speaker/73204703.png</t>
+  </si>
+  <si>
     <t>images_png/tv/277971948.png</t>
   </si>
   <si>
-    <t>images_png/tv/277989480.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/277991140.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/277972475.png</t>
-  </si>
-  <si>
     <t>images_png/phone/278098703.png</t>
   </si>
   <si>
-    <t>images_png/tv/276931435.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/276268195.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/275646608.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/275269812.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/275019168.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/248237801.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/276921311.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/276621107.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/275245456.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/276861683.png</t>
-  </si>
-  <si>
-    <t>images_png/tv/278077419.png</t>
+    <t>images_png/speaker/76062253.png</t>
+  </si>
+  <si>
+    <t>images_png/laptop/214863390.png</t>
+  </si>
+  <si>
+    <t>images_png/phone/277175913.png</t>
+  </si>
+  <si>
+    <t>images_png/phone/277063012.png</t>
+  </si>
+  <si>
+    <t>images_png/phone/276539826.png</t>
+  </si>
+  <si>
+    <t>images_png/phone/276110023.png</t>
+  </si>
+  <si>
+    <t>images_png/phone/252586291.png</t>
+  </si>
+  <si>
+    <t>images_png/phone/181927774.png</t>
+  </si>
+  <si>
+    <t>images_png/laptop/275854386.png</t>
+  </si>
+  <si>
+    <t>images_png/laptop/273187662.png</t>
+  </si>
+  <si>
+    <t>images_png/laptop/277912715.png</t>
+  </si>
+  <si>
+    <t>images_png/camera/275773160.png</t>
+  </si>
+  <si>
+    <t>images_png/laptop/277466579.png</t>
+  </si>
+  <si>
+    <t>images_png/laptop/276366329.png</t>
+  </si>
+  <si>
+    <t>images_png/camera/275255482.png</t>
+  </si>
+  <si>
+    <t>images_png/camera/274567496.png</t>
+  </si>
+  <si>
+    <t>images_png/camera/186103396.png</t>
   </si>
   <si>
     <t>images_png/camera/174896487.png</t>
   </si>
   <si>
-    <t>images_png/speaker/73204703.png</t>
-  </si>
-  <si>
-    <t>images_png/speaker/76062253.png</t>
-  </si>
-  <si>
-    <t>images_png/phone/277175913.png</t>
-  </si>
-  <si>
-    <t>images_png/phone/277063012.png</t>
-  </si>
-  <si>
-    <t>images_png/phone/276539826.png</t>
-  </si>
-  <si>
-    <t>images_png/phone/276110023.png</t>
-  </si>
-  <si>
-    <t>images_png/phone/252586291.png</t>
-  </si>
-  <si>
-    <t>images_png/phone/181927774.png</t>
-  </si>
-  <si>
-    <t>images_png/laptop/277961929.png</t>
-  </si>
-  <si>
-    <t>images_png/laptop/277953961.png</t>
-  </si>
-  <si>
-    <t>images_png/laptop/275854386.png</t>
-  </si>
-  <si>
-    <t>images_png/laptop/275382480.png</t>
-  </si>
-  <si>
-    <t>images_png/laptop/273187662.png</t>
-  </si>
-  <si>
-    <t>images_png/laptop/214863390.png</t>
-  </si>
-  <si>
-    <t>images_png/laptop/277912715.png</t>
-  </si>
-  <si>
-    <t>images_png/laptop/277466579.png</t>
-  </si>
-  <si>
-    <t>images_png/laptop/276366329.png</t>
-  </si>
-  <si>
     <t>images_png/camera/57071523.png</t>
   </si>
   <si>
     <t>images_png/camera/274069561.png</t>
-  </si>
-  <si>
-    <t>images_png/camera/275773160.png</t>
-  </si>
-  <si>
-    <t>images_png/speaker/276075466.png</t>
   </si>
   <si>
     <t>images_png/tv/275655645.png</t>
@@ -570,7 +570,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>7</v>
@@ -589,10 +589,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -600,10 +600,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -611,10 +611,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -622,10 +622,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -633,10 +633,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -644,10 +644,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -655,10 +655,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -666,10 +666,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -677,10 +677,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -688,10 +688,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -710,7 +710,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>3</v>
@@ -743,7 +743,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>3</v>
@@ -754,10 +754,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
         <v>20</v>
@@ -765,10 +765,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="s">
         <v>21</v>
@@ -776,7 +776,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -831,7 +831,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -853,7 +853,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -875,7 +875,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -886,7 +886,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -908,7 +908,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -919,7 +919,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -941,7 +941,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B36">
         <v>2</v>
@@ -952,7 +952,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="B37">
         <v>2</v>
@@ -963,7 +963,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B38">
         <v>2</v>
@@ -974,7 +974,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B39">
         <v>2</v>
@@ -985,7 +985,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B40">
         <v>2</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B41">
         <v>2</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B42">
         <v>2</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B43">
         <v>2</v>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B44">
         <v>2</v>
@@ -1040,7 +1040,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B45">
         <v>2</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B47">
         <v>2</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B48">
         <v>2</v>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B49">
         <v>2</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B50">
         <v>2</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B51">
         <v>2</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B52">
         <v>2</v>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B53">
         <v>2</v>
